--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.08894280991817</v>
+        <v>6.026953206611702</v>
       </c>
       <c r="D2" t="n">
-        <v>37.14528760337641</v>
+        <v>6.036109235548667</v>
       </c>
       <c r="E2" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F2" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.75781174152817</v>
+        <v>4.023144407998328</v>
       </c>
       <c r="D3" t="n">
-        <v>24.72174544316173</v>
+        <v>4.017283634513782</v>
       </c>
       <c r="E3" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F3" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.42217667357751</v>
+        <v>1.693603709456346</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7464736134262</v>
+        <v>1.746301962181757</v>
       </c>
       <c r="E4" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F4" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.452452320461283</v>
+        <v>0.8860235020749586</v>
       </c>
       <c r="D5" t="n">
-        <v>7.557957307824813</v>
+        <v>1.228168062521532</v>
       </c>
       <c r="E5" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F5" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.59626765813504</v>
+        <v>4.321893494446945</v>
       </c>
       <c r="D6" t="n">
-        <v>23.84510474198424</v>
+        <v>3.87482952057244</v>
       </c>
       <c r="E6" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F6" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.43689928620639</v>
+        <v>3.483496134008539</v>
       </c>
       <c r="D7" t="n">
-        <v>24.14089240769022</v>
+        <v>3.92289501624966</v>
       </c>
       <c r="E7" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F7" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.40086708342854</v>
+        <v>5.590140901057137</v>
       </c>
       <c r="D8" t="n">
-        <v>33.01379551513084</v>
+        <v>5.364741771208761</v>
       </c>
       <c r="E8" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F8" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07456456107424</v>
+        <v>4.237116741174564</v>
       </c>
       <c r="D9" t="n">
-        <v>28.55059607557637</v>
+        <v>4.63947186228116</v>
       </c>
       <c r="E9" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F9" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.7823925605079</v>
+        <v>4.514638791082534</v>
       </c>
       <c r="D10" t="n">
-        <v>28.4324869436793</v>
+        <v>4.620279128347887</v>
       </c>
       <c r="E10" t="n">
-        <v>9.660474975895211</v>
+        <v>1.569827183582972</v>
       </c>
       <c r="F10" t="n">
-        <v>9.070389943763416</v>
+        <v>1.473938365861555</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
